--- a/masters/grid_import_split/USGI_grid_26-27.xlsx
+++ b/masters/grid_import_split/USGI_grid_26-27.xlsx
@@ -780,7 +780,6 @@
           <t>4W</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>MOTOR</t>
@@ -788,29 +787,19 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>01-04-2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>31-03-2027</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Rate identical in source's 'Up to 5 Year' and 'Greater than 5 Year' age tables for Madhya Pradesh</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
         <v>0</v>
       </c>
@@ -822,23 +811,11 @@
           <t>Ton</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
           <t>State: Madhya Pradesh (full RTO list not expanded against RTO master)</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
         <v>25</v>
       </c>
@@ -847,32 +824,9 @@
           <t>OD (assumed — not explicitly labeled in source image)</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>25</v>
+      </c>
       <c r="BM2" t="inlineStr">
         <is>
           <t>6 policies: MP-10 Khargone, MP-14 Mandsaur, Alirajpur, Mandla, Mau x2 (Commercial/GCV/4W/1+1/Package) — GVW per vehicle unknown, so all bands listed</t>
@@ -915,7 +869,6 @@
           <t>4W</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>MOTOR</t>
@@ -923,29 +876,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>01-04-2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>31-03-2027</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Rate identical in source's 'Up to 5 Year' and 'Greater than 5 Year' age tables for Madhya Pradesh</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
         <v>3.5</v>
       </c>
@@ -957,23 +900,11 @@
           <t>Ton</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
           <t>State: Madhya Pradesh (full RTO list not expanded against RTO master)</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
         <v>18</v>
       </c>
@@ -982,32 +913,9 @@
           <t>OD (assumed — not explicitly labeled in source image)</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>18</v>
+      </c>
       <c r="BM3" t="inlineStr">
         <is>
           <t>6 policies: MP-10 Khargone, MP-14 Mandsaur, Alirajpur, Mandla, Mau x2 (Commercial/GCV/4W/1+1/Package) — GVW per vehicle unknown, so all bands listed</t>
@@ -1050,7 +958,6 @@
           <t>4W</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>MOTOR</t>
@@ -1058,29 +965,19 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>01-04-2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>31-03-2027</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Rate identical in source's 'Up to 5 Year' and 'Greater than 5 Year' age tables for Madhya Pradesh</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
         <v>7.5</v>
       </c>
@@ -1092,23 +989,11 @@
           <t>Ton</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
           <t>State: Madhya Pradesh (full RTO list not expanded against RTO master)</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
@@ -1117,32 +1002,9 @@
           <t>OD (assumed — not explicitly labeled in source image)</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
       <c r="BM4" t="inlineStr">
         <is>
           <t>6 policies: MP-10 Khargone, MP-14 Mandsaur, Alirajpur, Mandla, Mau x2 (Commercial/GCV/4W/1+1/Package) — GVW per vehicle unknown, so all bands listed</t>
@@ -1185,7 +1047,6 @@
           <t>4W</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>MOTOR</t>
@@ -1193,29 +1054,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>01-04-2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>31-03-2027</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Rate identical in source's 'Up to 5 Year' and 'Greater than 5 Year' age tables for Madhya Pradesh</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
         <v>12</v>
       </c>
@@ -1227,23 +1078,11 @@
           <t>Ton</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
           <t>State: Madhya Pradesh (full RTO list not expanded against RTO master)</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
@@ -1252,32 +1091,9 @@
           <t>OD (assumed — not explicitly labeled in source image)</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
       <c r="BM5" t="inlineStr">
         <is>
           <t>6 policies: MP-10 Khargone, MP-14 Mandsaur, Alirajpur, Mandla, Mau x2 (Commercial/GCV/4W/1+1/Package) — GVW per vehicle unknown, so all bands listed</t>
@@ -1320,7 +1136,6 @@
           <t>4W</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>MOTOR</t>
@@ -1328,29 +1143,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>01-04-2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>31-03-2027</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Rate identical in source's 'Up to 5 Year' and 'Greater than 5 Year' age tables for Madhya Pradesh</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
         <v>20</v>
       </c>
@@ -1362,23 +1167,11 @@
           <t>Ton</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
           <t>State: Madhya Pradesh (full RTO list not expanded against RTO master)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
@@ -1387,32 +1180,9 @@
           <t>OD (assumed — not explicitly labeled in source image)</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
       <c r="BM6" t="inlineStr">
         <is>
           <t>6 policies: MP-10 Khargone, MP-14 Mandsaur, Alirajpur, Mandla, Mau x2 (Commercial/GCV/4W/1+1/Package) — GVW per vehicle unknown, so all bands listed</t>
@@ -1455,7 +1225,6 @@
           <t>4W</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>MOTOR</t>
@@ -1463,29 +1232,19 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>01-04-2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>31-03-2027</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Rate identical in source's 'Up to 5 Year' and 'Greater than 5 Year' age tables for Madhya Pradesh</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
         <v>35</v>
       </c>
@@ -1497,23 +1256,11 @@
           <t>Ton</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
           <t>State: Madhya Pradesh (full RTO list not expanded against RTO master)</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
@@ -1522,32 +1269,9 @@
           <t>OD (assumed — not explicitly labeled in source image)</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
       <c r="BM7" t="inlineStr">
         <is>
           <t>6 policies: MP-10 Khargone, MP-14 Mandsaur, Alirajpur, Mandla, Mau x2 (Commercial/GCV/4W/1+1/Package) — GVW per vehicle unknown, so all bands listed</t>
@@ -1590,7 +1314,6 @@
           <t>4W</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>MOTOR</t>
@@ -1598,33 +1321,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>01-04-2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>31-03-2027</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Rate identical in source's 'Up to 5 Year' and 'Greater than 5 Year' age tables for Madhya Pradesh</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
         <v>45</v>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Ton</t>
@@ -1635,22 +1347,11 @@
           <t>45T Plus (no upper bound)</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
           <t>State: Madhya Pradesh (full RTO list not expanded against RTO master)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
@@ -1659,32 +1360,9 @@
           <t>OD (assumed — not explicitly labeled in source image)</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
       <c r="BM8" t="inlineStr">
         <is>
           <t>6 policies: MP-10 Khargone, MP-14 Mandsaur, Alirajpur, Mandla, Mau x2 (Commercial/GCV/4W/1+1/Package) — GVW per vehicle unknown, so all bands listed</t>
@@ -2088,43 +1766,26 @@
           <t>MOTOR</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-04-2026</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>31-03-2027</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>New and Old (rate identical)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
           <t>Madhya Pradesh / Bihar / Chhattisgarh / Uttar Pradesh / Maharashtra / Rajasthan — all 25%</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
         <v>0.25</v>
       </c>
@@ -2133,32 +1794,9 @@
           <t>Net Premium</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>0.25</v>
+      </c>
       <c r="BM2" t="n">
         <v>91</v>
       </c>
